--- a/jogos_2025-05-12.xlsx
+++ b/jogos_2025-05-12.xlsx
@@ -1068,13 +1068,13 @@
         <v>7.3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="R5" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S5" t="n">
         <v>2.5</v>
@@ -1086,13 +1086,13 @@
         <v>1.27</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X5" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Y5" t="n">
         <v>2.25</v>
@@ -1110,7 +1110,7 @@
         <v>2.27</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH5" t="n">
         <v>1.1</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45789.5</v>
@@ -1159,19 +1159,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>5.1</v>
       </c>
       <c r="O6" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S6" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.85</v>
+        <v>3.28</v>
       </c>
       <c r="U6" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="V6" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="X6" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="Y6" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['-1', '-1']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH6" t="n">
         <v>2.05</v>
       </c>
-      <c r="Z6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['-1', '-1']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>['-1']</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AI6" t="n">
-        <v>1.8</v>
+        <v>1.51</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.3</v>
+        <v>2.96</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45789.5</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,19 +1288,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
+        <v>3</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q7" t="n">
         <v>3.4</v>
       </c>
-      <c r="N7" t="n">
-        <v>4</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4.4</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="T7" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="V7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB7" t="n">
         <v>1.25</v>
       </c>
-      <c r="X7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AC7" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1', '-1']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.93</v>
+        <v>1.53</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45789.5</v>
@@ -1407,35 +1407,35 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="n">
         <v>1</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.18</v>
+        <v>2.69</v>
       </c>
       <c r="M8" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="N8" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="S8" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>3.66</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="V8" t="n">
         <v>1.07</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="X8" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="Y8" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>['25', '59', '73']</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI8" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>['-1']</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>['-1']</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AJ8" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45789.5</v>
@@ -1546,109 +1546,109 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Mladost Novi Sad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P9" t="n">
         <v>2</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="M9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
+        <v>8</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S9" t="n">
         <v>2.3</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.4</v>
-      </c>
       <c r="T9" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X9" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.51</v>
+        <v>2.84</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.09</v>
+        <v>2.71</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['-1', '-1']</t>
+          <t>['-1', '-1', '-1']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.96</v>
+        <v>4.45</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45789.5</v>
@@ -1665,26 +1665,26 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mladost Novi Sad</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
@@ -1701,65 +1701,65 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.6</v>
+        <v>2.18</v>
       </c>
       <c r="M10" t="n">
-        <v>3.77</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="O10" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="T10" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="V10" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W10" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="X10" t="n">
-        <v>2.37</v>
+        <v>2.88</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.84</v>
+        <v>2.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.71</v>
+        <v>1.91</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['-1', '-1', '-1']</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AJ10" t="n">
-        <v>4.45</v>
+        <v>2.75</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45789.5</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,25 +1804,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.69</v>
+        <v>1.67</v>
       </c>
       <c r="M11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T11" t="n">
         <v>2.75</v>
       </c>
-      <c r="N11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.66</v>
-      </c>
       <c r="U11" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="V11" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="W11" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="X11" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.69</v>
+        <v>1.92</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.41</v>
+        <v>1.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.1</v>
+        <v>3.45</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.61</v>
+        <v>1.94</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['12']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['25', '59', '73']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.46</v>
+        <v>1.93</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45789.5</v>
@@ -1923,32 +1923,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.28</v>
+        <v>1.82</v>
       </c>
       <c r="M12" t="n">
-        <v>3.71</v>
+        <v>3.26</v>
       </c>
       <c r="N12" t="n">
-        <v>2.88</v>
+        <v>4.1</v>
       </c>
       <c r="O12" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.54</v>
+        <v>4.33</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="T12" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="U12" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W12" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="X12" t="n">
-        <v>5</v>
+        <v>3.35</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.52</v>
+        <v>1.93</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['23', '50']</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['5', '63', '90+1']</t>
+          <t>['25']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AI12" t="n">
         <v>1.67</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45789.54166666666</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.43</v>
+        <v>2.8</v>
       </c>
       <c r="M13" t="n">
-        <v>4.26</v>
+        <v>2.65</v>
       </c>
       <c r="N13" t="n">
-        <v>4.9</v>
+        <v>2.65</v>
       </c>
       <c r="O13" t="n">
-        <v>1.89</v>
+        <v>3.55</v>
       </c>
       <c r="P13" t="n">
-        <v>2.41</v>
+        <v>1.78</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.55</v>
+        <v>3.55</v>
       </c>
       <c r="R13" t="n">
-        <v>1.26</v>
+        <v>1.59</v>
       </c>
       <c r="S13" t="n">
-        <v>3.04</v>
+        <v>2.25</v>
       </c>
       <c r="T13" t="n">
-        <v>2.35</v>
+        <v>3.9</v>
       </c>
       <c r="U13" t="n">
-        <v>1.53</v>
+        <v>1.19</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W13" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="X13" t="n">
-        <v>3.84</v>
+        <v>2.3</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.69</v>
+        <v>2.85</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.03</v>
+        <v>1.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.81</v>
+        <v>5.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.45</v>
+        <v>1.13</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['54']</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['60']</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.85</v>
+        <v>1.4</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.39</v>
+        <v>1.91</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.99</v>
+        <v>2.25</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45789.54166666666</v>
@@ -2181,32 +2181,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" t="n">
         <v>1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.82</v>
+        <v>2.28</v>
       </c>
       <c r="M14" t="n">
-        <v>3.26</v>
+        <v>3.71</v>
       </c>
       <c r="N14" t="n">
-        <v>4.1</v>
+        <v>2.88</v>
       </c>
       <c r="O14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P14" t="n">
         <v>2.4</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q14" t="n">
-        <v>4.33</v>
+        <v>3.54</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="V14" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="X14" t="n">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AC14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>['23', '50']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>['5', '63', '90+1']</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>['90+3']</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>['25']</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.85</v>
       </c>
       <c r="AI14" t="n">
         <v>1.67</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45789.54166666666</v>
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.25</v>
+        <v>1.46</v>
       </c>
       <c r="M15" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>1.85</v>
+        <v>4.6</v>
       </c>
       <c r="O15" t="n">
-        <v>3.62</v>
+        <v>1.92</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.47</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.32</v>
+        <v>5.05</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="S15" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>['31', '34', '42', '55']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>4</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>['19', '35']</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>2.2</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45789.54166666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,16 +2449,16 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>2</v>
@@ -2467,7 +2467,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.06</v>
+        <v>3.25</v>
       </c>
       <c r="M16" t="n">
-        <v>2.65</v>
+        <v>3.7</v>
       </c>
       <c r="N16" t="n">
-        <v>2.49</v>
+        <v>1.85</v>
       </c>
       <c r="O16" t="n">
-        <v>3.85</v>
+        <v>3.62</v>
       </c>
       <c r="P16" t="n">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.48</v>
+        <v>2.32</v>
       </c>
       <c r="R16" t="n">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="S16" t="n">
+        <v>4</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['19', '35']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>2.2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['58']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['45', '87']</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>2.3</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45789.54166666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,109 +2578,109 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="M17" t="n">
-        <v>2.65</v>
+        <v>3.47</v>
       </c>
       <c r="N17" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="O17" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC17" t="n">
         <v>1.78</v>
       </c>
-      <c r="Q17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W17" t="n">
+      <c r="AD17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['9', '16', '44', '45+2', '76']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['45+5', '65']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.52</v>
       </c>
-      <c r="X17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC17" t="n">
+      <c r="AI17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>['76']</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['53']</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>2.25</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45789.54166666666</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,22 +2836,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
         <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.56</v>
+        <v>3.06</v>
       </c>
       <c r="M19" t="n">
-        <v>3.47</v>
+        <v>2.65</v>
       </c>
       <c r="N19" t="n">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="O19" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="P19" t="n">
-        <v>2.09</v>
+        <v>1.74</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.38</v>
+        <v>3.48</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="S19" t="n">
-        <v>2.72</v>
+        <v>2.2</v>
       </c>
       <c r="T19" t="n">
-        <v>2.97</v>
+        <v>3.95</v>
       </c>
       <c r="U19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['58']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['45', '87']</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.36</v>
       </c>
-      <c r="V19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>['9', '16', '44', '45+2', '76']</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>['45+5', '65']</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AI19" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45789.54166666666</v>
@@ -2965,22 +2965,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2991,34 +2991,34 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="M20" t="n">
-        <v>4</v>
+        <v>4.26</v>
       </c>
       <c r="N20" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="O20" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="P20" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.05</v>
+        <v>6.55</v>
       </c>
       <c r="R20" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S20" t="n">
-        <v>3.28</v>
+        <v>3.04</v>
       </c>
       <c r="T20" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="U20" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="V20" t="n">
         <v>1.01</v>
@@ -3027,47 +3027,47 @@
         <v>1.18</v>
       </c>
       <c r="X20" t="n">
-        <v>4.5</v>
+        <v>3.84</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.48</v>
+        <v>1.69</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.16</v>
+        <v>2.81</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['31', '34', '42', '55']</t>
+          <t>['54']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['60']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AJ20" t="n">
-        <v>4</v>
+        <v>2.99</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45789.54166666666</v>
@@ -3342,35 +3342,35 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
         <v>1</v>
       </c>
-      <c r="H23" t="n">
-        <v>3</v>
-      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>3.04</v>
       </c>
       <c r="N23" t="n">
-        <v>3.55</v>
+        <v>3.97</v>
       </c>
       <c r="O23" t="n">
-        <v>2.27</v>
+        <v>2.65</v>
       </c>
       <c r="P23" t="n">
-        <v>2.42</v>
+        <v>1.97</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.62</v>
+        <v>4.9</v>
       </c>
       <c r="R23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U23" t="n">
         <v>1.25</v>
       </c>
-      <c r="S23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T23" t="n">
+      <c r="V23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>['41']</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>2.25</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>['80']</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>['15', '33', '83']</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>2.63</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45789.58333333334</v>
@@ -3471,35 +3471,35 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.15</v>
+        <v>8</v>
       </c>
       <c r="M24" t="n">
+        <v>5</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O24" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X24" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>['87']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>['47']</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI24" t="n">
         <v>3.6</v>
       </c>
-      <c r="N24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O24" t="n">
-        <v>3</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3</v>
-      </c>
-      <c r="R24" t="n">
+      <c r="AJ24" t="n">
         <v>1.3</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>['33', '45+5', '90+2']</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>2</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45789.58333333334</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,109 +3610,109 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" t="n">
         <v>1</v>
       </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
       <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="n">
         <v>1</v>
       </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="N25" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="O25" t="n">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="P25" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="R25" t="n">
         <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U25" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
         <v>1.05</v>
       </c>
       <c r="W25" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="X25" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="Z25" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>['12', '29', '63']</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>['26']</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.83</v>
       </c>
-      <c r="AA25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>['20']</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AI25" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45789.58333333334</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,25 +3739,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
         <v>1</v>
       </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD26" t="n">
         <v>1.95</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y26" t="n">
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>['7', '90+5']</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>2.3</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>['41']</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>2.25</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45789.58333333334</v>
@@ -3858,35 +3858,35 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.79</v>
+        <v>2.15</v>
       </c>
       <c r="M27" t="n">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="N27" t="n">
-        <v>2.18</v>
+        <v>2.9</v>
       </c>
       <c r="O27" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="P27" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S27" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="T27" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="U27" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="V27" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W27" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X27" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="Y27" t="n">
         <v>1.57</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.33</v>
+        <v>2.63</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AC27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>['33', '45+5', '90+2']</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD27" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>['55']</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>['23']</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AI27" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45789.58333333334</v>
@@ -3987,35 +3987,35 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>8</v>
+        <v>2.7</v>
       </c>
       <c r="M28" t="n">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="N28" t="n">
-        <v>1.26</v>
+        <v>2.57</v>
       </c>
       <c r="O28" t="n">
-        <v>7.37</v>
+        <v>3.1</v>
       </c>
       <c r="P28" t="n">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y28" t="n">
         <v>1.79</v>
       </c>
-      <c r="R28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X28" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y28" t="n">
+      <c r="Z28" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>['51', '70']</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>['5', '25', '37']</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z28" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>['87']</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>['47']</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AI28" t="n">
-        <v>3.6</v>
+        <v>2.05</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.3</v>
+        <v>1.83</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45789.58333333334</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,25 +4126,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>3.78</v>
       </c>
       <c r="N29" t="n">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="O29" t="n">
-        <v>4.2</v>
+        <v>3.07</v>
       </c>
       <c r="P29" t="n">
-        <v>1.97</v>
+        <v>2.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="R29" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="S29" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="T29" t="n">
-        <v>2.75</v>
+        <v>2.23</v>
       </c>
       <c r="U29" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="X29" t="n">
-        <v>3.02</v>
+        <v>4.9</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.13</v>
+        <v>1.57</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.71</v>
+        <v>2.4</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.55</v>
+        <v>2.33</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.21</v>
+        <v>1.6</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.89</v>
+        <v>2.55</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['55']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['57', '90+3']</t>
+          <t>['23']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45789.58333333334</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,25 +4255,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4281,80 +4281,80 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N30" t="n">
         <v>2.7</v>
       </c>
-      <c r="M30" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2.57</v>
-      </c>
       <c r="O30" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q30" t="n">
         <v>3.1</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3.08</v>
       </c>
       <c r="R30" t="n">
         <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="T30" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="U30" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="V30" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W30" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X30" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['51', '70']</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['5', '25', '37']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AI30" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AJ30" t="n">
         <v>1.83</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,19 +4384,19 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -4406,87 +4406,87 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>['-1', '-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45789.58333333334</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,109 +4513,109 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['80']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15', '33', '83']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45789.58333333334</v>
@@ -4632,119 +4632,119 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q33" t="n">
         <v>3</v>
       </c>
-      <c r="H33" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" t="n">
-        <v>2</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="M33" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="N33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>4.33</v>
-      </c>
       <c r="R33" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="T33" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="U33" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="V33" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="X33" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AC33" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>['-1']</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>['-1', '-1']</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ33" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>['12', '29', '63']</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>['26']</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>2.5</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45789.58333333334</v>
@@ -4761,32 +4761,32 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
         <v>2</v>
       </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="M34" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="N34" t="n">
-        <v>3.45</v>
+        <v>2.45</v>
       </c>
       <c r="O34" t="n">
-        <v>2.72</v>
+        <v>4.3</v>
       </c>
       <c r="P34" t="n">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="R34" t="n">
         <v>1.42</v>
       </c>
       <c r="S34" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="T34" t="n">
         <v>2.75</v>
       </c>
       <c r="U34" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V34" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W34" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X34" t="n">
-        <v>3.4</v>
+        <v>3.16</v>
       </c>
       <c r="Y34" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.96</v>
+        <v>1.57</v>
       </c>
       <c r="AA34" t="n">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['7', '90+5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['57', '90+3']</t>
         </is>
       </c>
       <c r="AG34" t="n">
         <v>1.33</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.67</v>
+        <v>1.31</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.73</v>
+        <v>2.34</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45789.58333333334</v>
@@ -5029,109 +5029,109 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
+        <v>6</v>
+      </c>
+      <c r="I36" t="n">
         <v>1</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>2</v>
       </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.3</v>
+        <v>6.2</v>
       </c>
       <c r="M36" t="n">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="N36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O36" t="n">
         <v>6.5</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1.73</v>
       </c>
       <c r="P36" t="n">
         <v>2.8</v>
       </c>
       <c r="Q36" t="n">
-        <v>6.25</v>
+        <v>1.78</v>
       </c>
       <c r="R36" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="S36" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="T36" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="V36" t="n">
         <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X36" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="Z36" t="n">
         <v>2.7</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>['45', '45+2', '75', '90+4']</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>['47']</t>
+          <t>['10', '38', '50', '52', '70', '90+4']</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AH36" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.53</v>
+        <v>3.25</v>
       </c>
       <c r="AJ36" t="n">
-        <v>2.7</v>
+        <v>1.38</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45789.60416666666</v>
@@ -5158,25 +5158,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G37" t="n">
+        <v>4</v>
+      </c>
+      <c r="H37" t="n">
         <v>1</v>
       </c>
-      <c r="H37" t="n">
-        <v>6</v>
-      </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>6.2</v>
+        <v>1.3</v>
       </c>
       <c r="M37" t="n">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="N37" t="n">
-        <v>1.33</v>
+        <v>6.5</v>
       </c>
       <c r="O37" t="n">
-        <v>6.5</v>
+        <v>1.73</v>
       </c>
       <c r="P37" t="n">
         <v>2.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.78</v>
+        <v>6.25</v>
       </c>
       <c r="R37" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="S37" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="T37" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="U37" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="V37" t="n">
         <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X37" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="Z37" t="n">
         <v>2.7</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>['45', '45+2', '75', '90+4']</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>['10', '38', '50', '52', '70', '90+4']</t>
+          <t>['47']</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="AI37" t="n">
-        <v>3.25</v>
+        <v>1.53</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.38</v>
+        <v>2.7</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45789.60416666666</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,109 +5287,109 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Fola Esch</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V38" t="n">
         <v>1</v>
       </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="M38" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="N38" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="O38" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R38" t="n">
+      <c r="W38" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X38" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB38" t="n">
         <v>1.28</v>
       </c>
-      <c r="S38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X38" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AC38" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
         <v>1.53</v>
       </c>
-      <c r="AD38" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>['-1']</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AH38" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AI38" t="n">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45789.625</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,16 +5416,16 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>1</v>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>2</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="P39" t="n">
         <v>1.97</v>
       </c>
-      <c r="M39" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N39" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="O39" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2</v>
-      </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R39" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S39" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="T39" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="U39" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V39" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W39" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="X39" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="AB39" t="n">
         <v>1.22</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>['62']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>['82']</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AJ39" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45789.625</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,16 +5545,16 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
         <v>1</v>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P40" t="n">
         <v>2</v>
       </c>
-      <c r="M40" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N40" t="n">
-        <v>3</v>
-      </c>
-      <c r="O40" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="P40" t="n">
-        <v>1.97</v>
-      </c>
       <c r="Q40" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R40" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W40" t="n">
         <v>1.4</v>
       </c>
-      <c r="S40" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.32</v>
-      </c>
       <c r="X40" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AB40" t="n">
         <v>1.22</v>
       </c>
       <c r="AC40" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>['62']</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>['82']</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH40" t="n">
         <v>1.7</v>
       </c>
-      <c r="AD40" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>['76']</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AI40" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45789.625</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,25 +5674,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
       <c r="M41" t="n">
-        <v>3.01</v>
+        <v>4.82</v>
       </c>
       <c r="N41" t="n">
-        <v>2.4</v>
+        <v>1.47</v>
       </c>
       <c r="O41" t="n">
-        <v>3.38</v>
+        <v>5</v>
       </c>
       <c r="P41" t="n">
-        <v>2.09</v>
+        <v>2.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.04</v>
+        <v>1.95</v>
       </c>
       <c r="R41" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X41" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>['16', '20', '27', '45+6', '52', '59', '64', '74', '90+4']</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AJ41" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S41" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X41" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1.89</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45789.625</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,25 +5803,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Fola Esch</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>5.3</v>
+        <v>3.14</v>
       </c>
       <c r="M42" t="n">
-        <v>4.82</v>
+        <v>3.81</v>
       </c>
       <c r="N42" t="n">
-        <v>1.47</v>
+        <v>1.93</v>
       </c>
       <c r="O42" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="P42" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q42" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q42" t="n">
-        <v>1.95</v>
-      </c>
       <c r="R42" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S42" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T42" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U42" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="V42" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W42" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X42" t="n">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="Y42" t="n">
         <v>1.57</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AB42" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC42" t="n">
         <v>1.53</v>
       </c>
-      <c r="AC42" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AD42" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5892,20 +5892,20 @@
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>['16', '20', '27', '45+6', '52', '59', '64', '74', '90+4']</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>2.53</v>
+        <v>1.7</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AI42" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45789.625</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,25 +6190,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Chabab Mohammedia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -6216,83 +6216,83 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.97</v>
+        <v>12.5</v>
       </c>
       <c r="M45" t="n">
-        <v>3.58</v>
+        <v>5.75</v>
       </c>
       <c r="N45" t="n">
-        <v>3.53</v>
+        <v>1.18</v>
       </c>
       <c r="O45" t="n">
-        <v>2.75</v>
+        <v>9</v>
       </c>
       <c r="P45" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.33</v>
+        <v>1.64</v>
       </c>
       <c r="R45" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S45" t="n">
-        <v>2.63</v>
+        <v>2.95</v>
       </c>
       <c r="T45" t="n">
-        <v>3.25</v>
+        <v>2.49</v>
       </c>
       <c r="U45" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="V45" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="W45" t="n">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="X45" t="n">
-        <v>2.8</v>
+        <v>4.15</v>
       </c>
       <c r="Y45" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.75</v>
+        <v>2.03</v>
       </c>
       <c r="AA45" t="n">
-        <v>3.8</v>
+        <v>2.45</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>['41', '52', '83']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['39', '45+4', '52', '54', '63', '83']</t>
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.29</v>
+        <v>4.4</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.67</v>
+        <v>5.35</v>
       </c>
       <c r="AJ45" t="n">
-        <v>2.5</v>
+        <v>1.16</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45789.66666666666</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,109 +6319,109 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Chabab Mohammedia</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="N46" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="O46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X46" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y46" t="n">
         <v>2</v>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L46" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="M46" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="N46" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="O46" t="n">
-        <v>9</v>
-      </c>
-      <c r="P46" t="n">
+      <c r="Z46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>['41', '52', '83']</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG46" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ46" t="n">
         <v>2.5</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S46" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X46" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>['39', '45+4', '52', '54', '63', '83']</t>
-        </is>
-      </c>
-      <c r="AG46" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>1.16</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45789.66666666666</v>
@@ -6577,22 +6577,22 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
         <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -6603,83 +6603,83 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.23</v>
+        <v>2.57</v>
       </c>
       <c r="M48" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="N48" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O48" t="n">
-        <v>2.93</v>
+        <v>3.6</v>
       </c>
       <c r="P48" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="R48" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="S48" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X48" t="n">
         <v>2.5</v>
       </c>
-      <c r="T48" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U48" t="n">
+      <c r="Y48" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
         <v>1.3</v>
       </c>
-      <c r="V48" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X48" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>['29']</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>['64']</t>
-        </is>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH48" t="n">
-        <v>1.54</v>
+        <v>1.39</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AJ48" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45789.8125</v>
@@ -6706,22 +6706,22 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
         <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -6732,83 +6732,83 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.57</v>
+        <v>2.23</v>
       </c>
       <c r="M49" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="N49" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O49" t="n">
-        <v>3.6</v>
+        <v>2.93</v>
       </c>
       <c r="P49" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="R49" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="S49" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="T49" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="U49" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X49" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>['29']</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>['64']</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
         <v>1.25</v>
       </c>
-      <c r="V49" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X49" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>['90+3']</t>
-        </is>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH49" t="n">
-        <v>1.39</v>
+        <v>1.54</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AJ49" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45789.8125</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,83 +6861,83 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="M50" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N50" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O50" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="P50" t="n">
         <v>1.85</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="R50" t="n">
         <v>1.58</v>
       </c>
       <c r="S50" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="T50" t="n">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="U50" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="V50" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="W50" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="X50" t="n">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="Y50" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG50" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ50" t="n">
         <v>2.88</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG50" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>2.63</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45789.83333333334</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="M51" t="n">
         <v>3</v>
       </c>
       <c r="N51" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="O51" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="P51" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.75</v>
+        <v>4.54</v>
       </c>
       <c r="R51" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="S51" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="T51" t="n">
-        <v>3.72</v>
+        <v>3.42</v>
       </c>
       <c r="U51" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="V51" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="W51" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="X51" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.71</v>
+        <v>2.35</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AA51" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,16 +7057,16 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AJ51" t="n">
-        <v>2.88</v>
+        <v>2.33</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45789.83333333334</v>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="M52" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N52" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O52" t="n">
         <v>3</v>
       </c>
-      <c r="N52" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O52" t="n">
-        <v>2.9</v>
-      </c>
       <c r="P52" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.54</v>
+        <v>4.2</v>
       </c>
       <c r="R52" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="S52" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="T52" t="n">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="U52" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="V52" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="W52" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="X52" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AA52" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,16 +7186,16 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AJ52" t="n">
-        <v>2.33</v>
+        <v>2.63</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45789.83333333334</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,16 +7351,16 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>CD El Nacional</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Cuniburo</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54" t="n">
         <v>1</v>
@@ -7377,83 +7377,83 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="M54" t="n">
-        <v>2.91</v>
+        <v>3.15</v>
       </c>
       <c r="N54" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="O54" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P54" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S54" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T54" t="n">
         <v>3</v>
       </c>
-      <c r="P54" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R54" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S54" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T54" t="n">
-        <v>3.42</v>
-      </c>
       <c r="U54" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="V54" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="W54" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="X54" t="n">
-        <v>2.55</v>
+        <v>3.08</v>
       </c>
       <c r="Y54" t="n">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AA54" t="n">
-        <v>4.6</v>
+        <v>3.34</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AC54" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD54" t="n">
         <v>2</v>
       </c>
-      <c r="AD54" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>['8']</t>
+          <t>['24', '62']</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['46']</t>
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AI54" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AJ54" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45789.875</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,16 +7480,16 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CD El Nacional</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cuniburo</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
         <v>1</v>
@@ -7506,83 +7506,83 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="M55" t="n">
-        <v>3.15</v>
+        <v>2.91</v>
       </c>
       <c r="N55" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="O55" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P55" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="R55" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="S55" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="T55" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="U55" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="V55" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W55" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="X55" t="n">
-        <v>3.08</v>
+        <v>2.55</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.01</v>
+        <v>2.5</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="AA55" t="n">
-        <v>3.34</v>
+        <v>4.6</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AC55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>['8']</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="AG55" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI55" t="n">
         <v>1.73</v>
       </c>
-      <c r="AD55" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>['24', '62']</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>['46']</t>
-        </is>
-      </c>
-      <c r="AG55" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AJ55" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AK55" s="3" t="n">
         <v>45789.875</v>
